--- a/24-06-26/Mubeen.xlsx
+++ b/24-06-26/Mubeen.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9D53F5-CB95-46F7-BBEE-65173310712A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD350B-B9DC-40B1-AF69-6F0D5E623BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3375,7 +3375,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3403,7 +3403,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4596,7 +4596,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4624,7 +4624,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5817,7 +5817,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5845,7 +5845,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7038,7 +7038,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7066,7 +7066,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8259,7 +8259,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8287,7 +8287,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9480,7 +9480,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9508,7 +9508,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10698,7 +10698,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10726,7 +10726,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11915,7 +11915,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11943,7 +11943,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13132,7 +13132,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13160,7 +13160,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14349,7 +14349,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14377,7 +14377,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18316,7 +18316,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18344,7 +18344,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19533,7 +19533,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19561,7 +19561,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20750,7 +20750,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20778,7 +20778,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21967,7 +21967,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21995,7 +21995,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23189,7 +23189,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23217,7 +23217,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -24656,7 +24656,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24684,7 +24684,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25886,7 +25886,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25914,7 +25914,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27107,7 +27107,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27135,7 +27135,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28327,7 +28327,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28355,7 +28355,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29552,7 +29552,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29580,7 +29580,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30773,7 +30773,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30801,7 +30801,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
